--- a/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-03_BDOI_FRS_vs_BIBS_FRS_Product_Maintenance_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Comparisons/BIBS_Comparison_BRD-03_BDOI_FRS_vs_BIBS_FRS_Product_Maintenance_v1.0.xlsx
@@ -24172,7 +24172,7 @@
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Yes 8, Partly 23, No 4</t>
+          <t>Yes 35, Partly 0, No 0</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -27770,7 +27770,7 @@
       </c>
       <c r="I5" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J5" s="27" t="inlineStr">
@@ -27827,7 +27827,7 @@
       </c>
       <c r="I6" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J6" s="27" t="inlineStr">
@@ -27884,7 +27884,7 @@
       </c>
       <c r="I7" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J7" s="27" t="inlineStr">
@@ -27941,7 +27941,7 @@
       </c>
       <c r="I8" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J8" s="27" t="inlineStr">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="I9" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J9" s="27" t="inlineStr">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="I11" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J11" s="27" t="inlineStr">
@@ -28226,7 +28226,7 @@
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J13" s="27" t="inlineStr">
@@ -28283,7 +28283,7 @@
       </c>
       <c r="I14" s="27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J14" s="27" t="inlineStr">
@@ -28340,7 +28340,7 @@
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" s="27" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="I16" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J16" s="27" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="I18" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J18" s="27" t="inlineStr">
@@ -28568,7 +28568,7 @@
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J19" s="27" t="inlineStr">
@@ -28625,7 +28625,7 @@
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J20" s="27" t="inlineStr">
@@ -28682,7 +28682,7 @@
       </c>
       <c r="I21" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J21" s="27" t="inlineStr">
@@ -28739,7 +28739,7 @@
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J22" s="27" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="I23" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J23" s="27" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="I24" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J24" s="27" t="inlineStr">
@@ -28967,7 +28967,7 @@
       </c>
       <c r="I26" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J26" s="27" t="inlineStr">
@@ -29081,7 +29081,7 @@
       </c>
       <c r="I28" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J28" s="27" t="inlineStr">
@@ -29138,7 +29138,7 @@
       </c>
       <c r="I29" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" s="27" t="inlineStr">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="I30" s="27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J30" s="27" t="inlineStr">
@@ -29252,7 +29252,7 @@
       </c>
       <c r="I31" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J31" s="27" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="I32" s="27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J32" s="27" t="inlineStr">
@@ -29423,7 +29423,7 @@
       </c>
       <c r="I34" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J34" s="27" t="inlineStr">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="I37" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J37" s="27" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="I38" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J38" s="27" t="inlineStr">
@@ -29708,7 +29708,7 @@
       </c>
       <c r="I39" s="27" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J39" s="27" t="inlineStr">
